--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1600,6 +1600,125 @@
           <t>Fågelkalendern</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123549039</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57660</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrfällsviken Camping, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>679268</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6987246</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nordingrå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>möjligt två individer</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Arne Hegemann</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Arne Hegemann</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>123549039</v>
       </c>
       <c r="B10" t="n">
-        <v>57660</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>123549039</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -1606,7 +1606,7 @@
         <v>123549039</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -1606,12 +1606,7 @@
         <v>123549039</v>
       </c>
       <c r="B10" t="n">
-        <v>57692</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45577-2021 artfynd.xlsx
+++ b/artfynd/A 45577-2021 artfynd.xlsx
@@ -1606,7 +1606,12 @@
         <v>123549039</v>
       </c>
       <c r="B10" t="n">
-        <v>58076</v>
+        <v>57692</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
